--- a/survey_templates/020_database_concepts_checklist--survey_templates.xlsx
+++ b/survey_templates/020_database_concepts_checklist--survey_templates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,12 +510,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_1</t>
+          <t>page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is a database</t>
+          <t>1. What is the primary function of a database?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -533,12 +533,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_2</t>
+          <t>page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is a database</t>
+          <t>2. What are the key elements of a database design?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_3</t>
+          <t>page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is database security</t>
+          <t>3. What is the difference between a database and a data warehouse?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,12 +579,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_4</t>
+          <t>page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is database security</t>
+          <t>4. How does data integrity impact database performance?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_5</t>
+          <t>page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is data modeling</t>
+          <t>5. What is the goal of database normalization?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_6</t>
+          <t>page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is data modeling</t>
+          <t>6. What is the relationship between database modeling and database design?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -648,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_7</t>
+          <t>page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is data integrity</t>
+          <t>7. How does database administration impact database performance?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_8</t>
+          <t>page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is data integrity</t>
+          <t>8. What is the role of database security in ensuring data protection?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_9</t>
+          <t>page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is normalization</t>
+          <t>9. How does data warehousing impact business decision-making?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_10</t>
+          <t>page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is normalization</t>
+          <t>10. What is the importance of data mining in data analysis?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_11</t>
+          <t>page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is data modeling in a database</t>
+          <t>11. How does OLAP (Online Analytical Processing) enhance data analysis?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -763,12 +763,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_12</t>
+          <t>page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is data modeling in a database</t>
+          <t>12. What is the key difference between data modeling and data warehousing?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_13</t>
+          <t>page_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is normalization in a database</t>
+          <t>13. What is the purpose of database design?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_14</t>
+          <t>page_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What is normalization in a database</t>
+          <t>14. What are the key factors that affect database performance?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_15</t>
+          <t>page_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is database design</t>
+          <t>15. What is the role of database administrator?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -855,12 +855,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_16</t>
+          <t>page_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is database design</t>
+          <t>16. What is the process of data normalization?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_17</t>
+          <t>page_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What is database administration</t>
+          <t>17. How does data quality impact database performance?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -901,177 +901,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>database_concepts_checklist_18</t>
+          <t>page_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is database administration</t>
+          <t>18. What is the key difference between OLAP and data mining?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>database_concepts_checklist_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What is data warehousing</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>database_concepts_checklist_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What is data warehousing</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>database_concepts_checklist_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What is OLAP</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>database_concepts_checklist_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is OLAP</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>database_concepts_checklist_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What is data mining</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>database_concepts_checklist_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is data mining</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>database_concepts_checklist_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What is data modeling and design</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
